--- a/docking_station/Hardware/reference/Docking_Station_BOM.xlsx
+++ b/docking_station/Hardware/reference/Docking_Station_BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asiadel\Documents\FIRO\firo_electronics\docking_station\Hardware\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC02F7F-FCAD-4635-B7CB-F38EB36596DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A512F426-0A44-42AB-8965-74E867812552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="113">
   <si>
     <t>Name</t>
   </si>
@@ -252,9 +252,6 @@
   </si>
   <si>
     <t>Thick Film Resistor, 1k2, ± 1%, 500 mW, 1206</t>
-  </si>
-  <si>
-    <t>https://de.farnell.com/en-DE/walsin/wf12p1201ftl/res-1k2-1-0-5w-1206-thick-film/dp/2670351</t>
   </si>
   <si>
     <t>PANASONIC ERJP06F2400V</t>
@@ -287,15 +284,6 @@
     <t>https://de.farnell.com/en-DE/panasonic/erjp06f2400v/res-240r-1-0-5w-0805-thick-film/dp/1894176</t>
   </si>
   <si>
-    <t>VISHAY MCS0402MD1001DE000</t>
-  </si>
-  <si>
-    <t>Thin Film Precision Resistor, 1 k, ± 0.5%, 0402</t>
-  </si>
-  <si>
-    <t>https://de.farnell.com/en-DE/vishay/mcs0402md1001de000/res-1k-0-5-0-1w-thin-film-0402/dp/4139935</t>
-  </si>
-  <si>
     <t>BOURNS CRT0402-DZ-1003GAS</t>
   </si>
   <si>
@@ -387,6 +375,39 @@
   <si>
     <t>Fuse, Fast Acting, 12.5 A, 5mm x 20mm</t>
   </si>
+  <si>
+    <t>https://de.farnell.com/en-DE/vishay/vj0805a102gxxpw1bc/cap-1000pf-25v-2-c0g-np0-0805/dp/2896470</t>
+  </si>
+  <si>
+    <t>MURATA GCJ219R71H334KA12D</t>
+  </si>
+  <si>
+    <t>MLCC, 0.33 µF, 50 V, 0805, ± 10%, X7R</t>
+  </si>
+  <si>
+    <t>https://de.farnell.com/en-DE/murata/gcj219r71h334ka12d/cap-aec-q200-0-33uf-50v-mlcc-0805/dp/3581154</t>
+  </si>
+  <si>
+    <t>RELPOL R40N-3021-85-1024</t>
+  </si>
+  <si>
+    <t>https://www.relpol.pl/en/Products/High-power-Relays/Industrial-relays-R40N/2614823-R40N-3021-85-1024</t>
+  </si>
+  <si>
+    <t>DO NOT BUY</t>
+  </si>
+  <si>
+    <t>Relay; SPST-NO; 24VDC; 40A; R40N; PCB; 0.9W</t>
+  </si>
+  <si>
+    <t>YAGEO RT0402BRD074K7L</t>
+  </si>
+  <si>
+    <t>Thin Film Resistor, 4k7, ± 0.1%, 62.5 mW, 0402</t>
+  </si>
+  <si>
+    <t>https://de.farnell.com/en-DE/yageo/rt0402brd074k7l/res-4k7-0-1-1-16w-0402-thin-film/dp/3496522</t>
+  </si>
 </sst>
 </file>
 
@@ -395,7 +416,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -439,6 +460,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -511,11 +538,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -891,846 +915,893 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="42.26953125" customWidth="1"/>
     <col min="2" max="2" width="38.36328125" customWidth="1"/>
-    <col min="3" max="3" width="92" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" customWidth="1"/>
+    <col min="3" max="3" width="100.26953125" customWidth="1"/>
+    <col min="4" max="4" width="4.90625" customWidth="1"/>
     <col min="5" max="5" width="7.81640625" customWidth="1"/>
     <col min="6" max="6" width="13.54296875" customWidth="1"/>
     <col min="7" max="7" width="2.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="23" t="s">
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="23"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="7">
         <v>2.4500000000000002</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="5">
         <v>5</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="8">
         <f t="shared" ref="F2:F10" si="0">D2*E2</f>
         <v>12.25</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="7">
         <v>0.308</v>
       </c>
-      <c r="E3" s="8">
-        <v>1</v>
-      </c>
-      <c r="F3" s="11">
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8">
         <f t="shared" si="0"/>
         <v>0.308</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="7">
         <v>3.98</v>
       </c>
-      <c r="E4" s="8">
-        <v>1</v>
-      </c>
-      <c r="F4" s="11">
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8">
         <f t="shared" si="0"/>
         <v>3.98</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="7">
         <v>6.24</v>
       </c>
-      <c r="E5" s="8">
-        <v>1</v>
-      </c>
-      <c r="F5" s="11">
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8">
         <f t="shared" si="0"/>
         <v>6.24</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="7">
         <v>0.67300000000000004</v>
       </c>
-      <c r="E6" s="8">
-        <v>1</v>
-      </c>
-      <c r="F6" s="11">
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8">
         <f t="shared" si="0"/>
         <v>0.67300000000000004</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="7">
         <v>0.51600000000000001</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="5">
         <v>3</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="8">
         <f t="shared" si="0"/>
         <v>1.548</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="11">
         <v>0.35299999999999998</v>
       </c>
-      <c r="E8" s="12">
-        <v>1</v>
-      </c>
-      <c r="F8" s="15">
+      <c r="E8" s="9">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12">
         <f t="shared" si="0"/>
         <v>0.35299999999999998</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="11">
         <v>0.36499999999999999</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="9">
         <v>2</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="12">
         <f t="shared" si="0"/>
         <v>0.73</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="11">
         <v>1.46</v>
       </c>
-      <c r="E10" s="12">
-        <v>9</v>
-      </c>
-      <c r="F10" s="15">
+      <c r="E10" s="9">
+        <v>9</v>
+      </c>
+      <c r="F10" s="12">
         <f t="shared" si="0"/>
         <v>13.14</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="11">
         <v>9.4E-2</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="9">
         <v>4</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="12">
         <f t="shared" ref="F11:F12" si="1">D11*E11</f>
         <v>0.376</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="15">
         <v>1.34</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="13">
         <v>2</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="16">
         <f t="shared" si="1"/>
         <v>2.68</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="15">
         <v>0.17499999999999999</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="13">
         <v>6</v>
       </c>
-      <c r="F13" s="19">
-        <f t="shared" ref="F13:F27" si="2">D13*E13</f>
+      <c r="F13" s="16">
+        <f t="shared" ref="F13:F17" si="2">D13*E13</f>
         <v>1.0499999999999998</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="15">
         <v>0.13100000000000001</v>
       </c>
-      <c r="E14" s="16">
-        <v>1</v>
-      </c>
-      <c r="F14" s="19">
+      <c r="E14" s="13">
+        <v>1</v>
+      </c>
+      <c r="F14" s="16">
         <f t="shared" si="2"/>
         <v>0.13100000000000001</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="36" t="s">
+      <c r="A15" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="15">
         <v>0.48199999999999998</v>
       </c>
-      <c r="E15" s="16">
-        <v>1</v>
-      </c>
-      <c r="F15" s="19">
+      <c r="E15" s="13">
+        <v>1</v>
+      </c>
+      <c r="F15" s="16">
         <f t="shared" si="2"/>
         <v>0.48199999999999998</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" s="18">
+      <c r="C16" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="15">
         <v>3.18</v>
       </c>
-      <c r="E16" s="16">
-        <v>1</v>
-      </c>
-      <c r="F16" s="19">
+      <c r="E16" s="13">
+        <v>1</v>
+      </c>
+      <c r="F16" s="16">
         <f t="shared" si="2"/>
         <v>3.18</v>
       </c>
-      <c r="G16" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="22" t="s">
+      <c r="G16" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="15">
         <v>0.121</v>
       </c>
-      <c r="E17" s="16">
-        <v>1</v>
-      </c>
-      <c r="F17" s="19">
+      <c r="E17" s="13">
+        <v>1</v>
+      </c>
+      <c r="F17" s="16">
         <f t="shared" si="2"/>
         <v>0.121</v>
       </c>
-      <c r="G17" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="22" t="s">
+      <c r="G17" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="15">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="E18" s="13">
+        <v>1</v>
+      </c>
+      <c r="F18" s="16">
+        <f t="shared" ref="F18" si="3">D18*E18</f>
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B19" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C19" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" s="15">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E19" s="13">
+        <v>2</v>
+      </c>
+      <c r="F19" s="16">
+        <f>D19*E19</f>
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="18">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="E18" s="16">
+      <c r="B20" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="15">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E20" s="13">
+        <v>4</v>
+      </c>
+      <c r="F20" s="16">
+        <f>D20*E20</f>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="15">
+        <v>6.2E-2</v>
+      </c>
+      <c r="E21" s="13">
         <v>2</v>
       </c>
-      <c r="F18" s="19">
-        <f t="shared" si="2"/>
-        <v>5.8000000000000003E-2</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="18">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E19" s="16">
+      <c r="F21" s="16">
+        <f>D21*E21</f>
+        <v>0.124</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="15">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="E22" s="13">
         <v>4</v>
       </c>
-      <c r="F19" s="19">
-        <f t="shared" si="2"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="18">
-        <v>8.8999999999999996E-2</v>
-      </c>
-      <c r="E20" s="16">
+      <c r="F22" s="16">
+        <f>D22*E22</f>
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="15">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="E23" s="13">
+        <v>1</v>
+      </c>
+      <c r="F23" s="16">
+        <f>D23*E23</f>
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="15">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="E24" s="13">
+        <v>1</v>
+      </c>
+      <c r="F24" s="16">
+        <f>D24*E24</f>
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="15">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="E25" s="13">
         <v>2</v>
       </c>
-      <c r="F20" s="19">
-        <f t="shared" si="2"/>
-        <v>0.17799999999999999</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="18">
-        <v>6.2E-2</v>
-      </c>
-      <c r="E21" s="16">
+      <c r="F25" s="16">
+        <f>D25*E25</f>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="15">
+        <v>4.7E-2</v>
+      </c>
+      <c r="E26" s="13">
+        <v>1</v>
+      </c>
+      <c r="F26" s="16">
+        <f>D26*E26</f>
+        <v>4.7E-2</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="E27" s="13">
         <v>2</v>
       </c>
-      <c r="F21" s="19">
-        <f t="shared" si="2"/>
-        <v>0.124</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" s="18">
-        <v>8.7999999999999995E-2</v>
-      </c>
-      <c r="E22" s="16">
-        <v>4</v>
-      </c>
-      <c r="F22" s="19">
-        <f t="shared" si="2"/>
-        <v>0.35199999999999998</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" s="18">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="E23" s="16">
-        <v>1</v>
-      </c>
-      <c r="F23" s="19">
-        <f t="shared" si="2"/>
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" s="18">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="E24" s="16">
-        <v>1</v>
-      </c>
-      <c r="F24" s="19">
-        <f t="shared" si="2"/>
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" s="18">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="E25" s="16">
+      <c r="F27" s="16">
+        <f>D27*E27</f>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="E28" s="13">
         <v>2</v>
       </c>
-      <c r="F25" s="19">
-        <f t="shared" si="2"/>
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="G25" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="D26" s="18">
-        <v>4.7E-2</v>
-      </c>
-      <c r="E26" s="16">
-        <v>1</v>
-      </c>
-      <c r="F26" s="19">
-        <f t="shared" si="2"/>
-        <v>4.7E-2</v>
-      </c>
-      <c r="G26" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" s="36" t="s">
+      <c r="F28" s="16">
+        <f>D28*E28</f>
+        <v>0.2</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3">
+        <f>D29*E29</f>
+        <v>0.85</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3">
+        <f>D30*E30</f>
+        <v>0.95</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" s="2">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3">
+        <f>D31*E31</f>
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="24">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="E32" s="22">
+        <v>3</v>
+      </c>
+      <c r="F32" s="23">
+        <f>D32*E32</f>
+        <v>0.504</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="24">
+        <v>0.125</v>
+      </c>
+      <c r="E33" s="22">
+        <v>2</v>
+      </c>
+      <c r="F33" s="23">
+        <f t="shared" ref="F33:F34" si="4">D33*E33</f>
+        <v>0.25</v>
+      </c>
+      <c r="G33" s="22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="31">
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="E34" s="26">
+        <v>1</v>
+      </c>
+      <c r="F34" s="27">
+        <f t="shared" si="4"/>
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="G34" s="26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D35" s="31">
+        <v>1.29</v>
+      </c>
+      <c r="E35" s="26">
+        <v>1</v>
+      </c>
+      <c r="F35" s="27">
+        <f t="shared" ref="F35" si="5">D35*E35</f>
+        <v>1.29</v>
+      </c>
+      <c r="G35" s="26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="D27" s="18">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="E27" s="16">
-        <v>1</v>
-      </c>
-      <c r="F27" s="19">
-        <f t="shared" si="2"/>
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="E28" s="4">
-        <v>1</v>
-      </c>
-      <c r="F28" s="6">
-        <f>D28*E28</f>
-        <v>0.85</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="E29" s="4">
-        <v>1</v>
-      </c>
-      <c r="F29" s="6">
-        <f>D29*E29</f>
-        <v>0.95</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="27">
-        <v>0.16800000000000001</v>
-      </c>
-      <c r="E30" s="25">
-        <v>3</v>
-      </c>
-      <c r="F30" s="26">
-        <f>D30*E30</f>
-        <v>0.504</v>
-      </c>
-      <c r="G30" s="25" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="27">
-        <v>0.125</v>
-      </c>
-      <c r="E31" s="25">
-        <v>2</v>
-      </c>
-      <c r="F31" s="26">
-        <f t="shared" ref="F31:F32" si="3">D31*E31</f>
-        <v>0.25</v>
-      </c>
-      <c r="G31" s="25" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="D32" s="34">
-        <v>0.82799999999999996</v>
-      </c>
-      <c r="E32" s="29">
-        <v>1</v>
-      </c>
-      <c r="F32" s="30">
-        <f t="shared" si="3"/>
-        <v>0.82799999999999996</v>
-      </c>
-      <c r="G32" s="29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="34">
-        <v>1.29</v>
-      </c>
-      <c r="E33" s="29">
-        <v>1</v>
-      </c>
-      <c r="F33" s="30">
-        <f t="shared" ref="F33" si="4">D33*E33</f>
-        <v>1.29</v>
-      </c>
-      <c r="G33" s="29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="D34" s="34">
+      <c r="D36" s="31">
         <v>0.36699999999999999</v>
       </c>
-      <c r="E34" s="29">
-        <v>1</v>
-      </c>
-      <c r="F34" s="30">
-        <f t="shared" ref="F34" si="5">D34*E34</f>
+      <c r="E36" s="26">
+        <v>1</v>
+      </c>
+      <c r="F36" s="27">
+        <f t="shared" ref="F36" si="6">D36*E36</f>
         <v>0.36699999999999999</v>
       </c>
-      <c r="G34" s="29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="F35" s="7">
-        <f>SUM(F2:F34)</f>
-        <v>53.426000000000009</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C36" s="1"/>
-      <c r="D36" s="3"/>
-      <c r="F36" s="2"/>
+      <c r="G36" s="26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F37" s="4">
+        <f>SUM(F2:F36)</f>
+        <v>57.871000000000016</v>
+      </c>
+      <c r="G37" s="34" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C10" r:id="rId1" xr:uid="{31761AB8-3D78-4C08-AAB7-B1B624F5516A}"/>
     <hyperlink ref="C2" r:id="rId2" xr:uid="{C1D6BB8F-4997-4BAB-AAF5-1A80B8A4920C}"/>
@@ -1743,28 +1814,28 @@
     <hyperlink ref="C11" r:id="rId9" xr:uid="{B58639FA-8A6B-4D3F-8892-98D6CD897662}"/>
     <hyperlink ref="C12" r:id="rId10" xr:uid="{2AB3FE37-A900-4C37-96E3-F2D321E450C5}"/>
     <hyperlink ref="C9" r:id="rId11" xr:uid="{AEE86DFC-B231-4D03-84CA-36120F849FA6}"/>
-    <hyperlink ref="C30" r:id="rId12" xr:uid="{7D44598B-41A4-412B-89BC-1954C7D2B637}"/>
-    <hyperlink ref="C31" r:id="rId13" xr:uid="{04CE631E-E47F-4F03-89FC-780E48EB194A}"/>
-    <hyperlink ref="C29" r:id="rId14" xr:uid="{6BD2DC9E-A067-4259-9725-F6E7AE61C829}"/>
-    <hyperlink ref="C33" r:id="rId15" xr:uid="{A06D36CF-69EE-41F4-B9B0-6C0813A1980C}"/>
-    <hyperlink ref="C28" r:id="rId16" xr:uid="{3F20F69A-C501-43FF-83B3-F7DB1604587E}"/>
+    <hyperlink ref="C32" r:id="rId12" xr:uid="{7D44598B-41A4-412B-89BC-1954C7D2B637}"/>
+    <hyperlink ref="C33" r:id="rId13" xr:uid="{04CE631E-E47F-4F03-89FC-780E48EB194A}"/>
+    <hyperlink ref="C30" r:id="rId14" xr:uid="{6BD2DC9E-A067-4259-9725-F6E7AE61C829}"/>
+    <hyperlink ref="C35" r:id="rId15" xr:uid="{A06D36CF-69EE-41F4-B9B0-6C0813A1980C}"/>
+    <hyperlink ref="C29" r:id="rId16" xr:uid="{3F20F69A-C501-43FF-83B3-F7DB1604587E}"/>
     <hyperlink ref="C13" r:id="rId17" xr:uid="{F507A98C-B1F7-407A-9C9E-B41E4B2E09F6}"/>
     <hyperlink ref="C14" r:id="rId18" xr:uid="{F2AC6605-395D-4E2D-84FC-8618A9362968}"/>
     <hyperlink ref="C15" r:id="rId19" xr:uid="{C27C3A31-4687-497C-96AA-AA15F0FA40F3}"/>
     <hyperlink ref="C16" r:id="rId20" xr:uid="{4EB417DF-5F79-4FC3-BF5D-8E1100D18C8C}"/>
     <hyperlink ref="C17" r:id="rId21" xr:uid="{AADAF6B6-DC7D-49E0-8076-D9013C9D43E2}"/>
-    <hyperlink ref="C18" r:id="rId22" xr:uid="{6849A4A4-5E7E-42B2-82D5-9C6CFACDDA4E}"/>
-    <hyperlink ref="C19" r:id="rId23" xr:uid="{ABECD05F-28DC-49E4-B70E-D303248532DC}"/>
-    <hyperlink ref="C20" r:id="rId24" xr:uid="{CAF93C52-EA26-473A-91A2-855CC4699F13}"/>
-    <hyperlink ref="C21" r:id="rId25" xr:uid="{5CD7CD11-EF66-4DA7-8B90-47F7747F6FE2}"/>
-    <hyperlink ref="C22" r:id="rId26" xr:uid="{5F894464-016C-4FC7-AE87-FC37C6ED02E1}"/>
-    <hyperlink ref="C23" r:id="rId27" xr:uid="{E3FF1BDF-75A1-41ED-8065-AE93E2CD6B63}"/>
-    <hyperlink ref="C24" r:id="rId28" xr:uid="{82A0BF17-C825-4CB6-8D23-9D2BFFEF0C93}"/>
-    <hyperlink ref="C25" r:id="rId29" xr:uid="{FCC12E96-E5DC-42EC-BF82-C15086A611F0}"/>
-    <hyperlink ref="C26" r:id="rId30" xr:uid="{93149CF0-7A81-4EB0-8529-1F2B21B9ADBB}"/>
-    <hyperlink ref="C27" r:id="rId31" xr:uid="{3A30AE01-0625-4E71-925F-0987CC3B2FDB}"/>
-    <hyperlink ref="C34" r:id="rId32" xr:uid="{981595ED-2FB0-4D7D-B135-890AA024614C}"/>
-    <hyperlink ref="C32" r:id="rId33" xr:uid="{E5EE0C9F-4C72-4CE4-B37A-718B28D05905}"/>
+    <hyperlink ref="C20" r:id="rId22" xr:uid="{ABECD05F-28DC-49E4-B70E-D303248532DC}"/>
+    <hyperlink ref="C21" r:id="rId23" xr:uid="{5CD7CD11-EF66-4DA7-8B90-47F7747F6FE2}"/>
+    <hyperlink ref="C22" r:id="rId24" xr:uid="{5F894464-016C-4FC7-AE87-FC37C6ED02E1}"/>
+    <hyperlink ref="C23" r:id="rId25" xr:uid="{E3FF1BDF-75A1-41ED-8065-AE93E2CD6B63}"/>
+    <hyperlink ref="C24" r:id="rId26" xr:uid="{82A0BF17-C825-4CB6-8D23-9D2BFFEF0C93}"/>
+    <hyperlink ref="C25" r:id="rId27" xr:uid="{FCC12E96-E5DC-42EC-BF82-C15086A611F0}"/>
+    <hyperlink ref="C26" r:id="rId28" xr:uid="{93149CF0-7A81-4EB0-8529-1F2B21B9ADBB}"/>
+    <hyperlink ref="C27" r:id="rId29" xr:uid="{3A30AE01-0625-4E71-925F-0987CC3B2FDB}"/>
+    <hyperlink ref="C36" r:id="rId30" xr:uid="{981595ED-2FB0-4D7D-B135-890AA024614C}"/>
+    <hyperlink ref="C34" r:id="rId31" xr:uid="{E5EE0C9F-4C72-4CE4-B37A-718B28D05905}"/>
+    <hyperlink ref="C18" r:id="rId32" display="https://de.farnell.com/en-DE/vishay/vj0805a102gxxpw1bc/cap-1000pf-25v-2-c0g-np0-0805/dp/2896469" xr:uid="{9FFE2EA7-BA3C-4C10-ABCF-6ED930668B13}"/>
+    <hyperlink ref="C31" r:id="rId33" xr:uid="{C2615CAE-FFFA-4D7E-A096-F69F531AB976}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
